--- a/final_data_pipeline/output/311411longform.xlsx
+++ b/final_data_pipeline/output/311411longform.xlsx
@@ -903,7 +903,7 @@
         <v>115</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -989,7 +989,7 @@
         <v>115</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1072,7 +1072,7 @@
         <v>115</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1155,7 +1155,7 @@
         <v>115</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -4923,7 +4923,7 @@
         <v>115</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -5009,7 +5009,7 @@
         <v>115</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -5092,7 +5092,7 @@
         <v>115</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5175,7 +5175,7 @@
         <v>115</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5261,7 +5261,7 @@
         <v>115</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5344,7 +5344,7 @@
         <v>115</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5427,7 +5427,7 @@
         <v>115</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -5510,7 +5510,7 @@
         <v>115</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -5596,7 +5596,7 @@
         <v>115</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -5685,7 +5685,7 @@
         <v>115</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -5777,7 +5777,7 @@
         <v>115</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -5869,7 +5869,7 @@
         <v>115</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -5961,7 +5961,7 @@
         <v>115</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6053,7 +6053,7 @@
         <v>115</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6145,7 +6145,7 @@
         <v>115</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6237,7 +6237,7 @@
         <v>115</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6329,7 +6329,7 @@
         <v>115</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -6418,7 +6418,7 @@
         <v>115</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB67">
         <v>8000</v>
@@ -6507,7 +6507,7 @@
         <v>115</v>
       </c>
       <c r="AA68">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB68">
         <v>8000</v>
@@ -6596,7 +6596,7 @@
         <v>115</v>
       </c>
       <c r="AA69">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB69">
         <v>8000</v>
@@ -6685,7 +6685,7 @@
         <v>115</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -6768,7 +6768,7 @@
         <v>115</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -6857,7 +6857,7 @@
         <v>115</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -6946,7 +6946,7 @@
         <v>115</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -7035,7 +7035,7 @@
         <v>115</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -7118,7 +7118,7 @@
         <v>115</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7207,7 +7207,7 @@
         <v>115</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -7296,7 +7296,7 @@
         <v>115</v>
       </c>
       <c r="AA77">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB77">
         <v>8000</v>
@@ -7385,7 +7385,7 @@
         <v>115</v>
       </c>
       <c r="AA78">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB78">
         <v>8000</v>
@@ -7474,7 +7474,7 @@
         <v>115</v>
       </c>
       <c r="AA79">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB79">
         <v>8000</v>
@@ -7563,7 +7563,7 @@
         <v>115</v>
       </c>
       <c r="AA80">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB80">
         <v>8000</v>
@@ -7652,7 +7652,7 @@
         <v>115</v>
       </c>
       <c r="AA81">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB81">
         <v>8000</v>
@@ -7741,7 +7741,7 @@
         <v>115</v>
       </c>
       <c r="AA82">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB82">
         <v>8000</v>
@@ -7830,7 +7830,7 @@
         <v>115</v>
       </c>
       <c r="AA83">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB83">
         <v>8000</v>
@@ -7919,7 +7919,7 @@
         <v>115</v>
       </c>
       <c r="AA84">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB84">
         <v>8000</v>
@@ -8008,7 +8008,7 @@
         <v>115</v>
       </c>
       <c r="AA85">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB85">
         <v>8000</v>
@@ -8097,7 +8097,7 @@
         <v>115</v>
       </c>
       <c r="AA86">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB86">
         <v>8000</v>
@@ -8186,7 +8186,7 @@
         <v>115</v>
       </c>
       <c r="AA87">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB87">
         <v>8000</v>
@@ -8269,7 +8269,7 @@
         <v>115</v>
       </c>
       <c r="AA88">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB88">
         <v>8000</v>
@@ -8358,7 +8358,7 @@
         <v>115</v>
       </c>
       <c r="AA89">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB89">
         <v>8000</v>
@@ -8441,7 +8441,7 @@
         <v>115</v>
       </c>
       <c r="AA90">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB90">
         <v>8000</v>
@@ -8530,7 +8530,7 @@
         <v>115</v>
       </c>
       <c r="AA91">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB91">
         <v>8000</v>
@@ -8613,7 +8613,7 @@
         <v>115</v>
       </c>
       <c r="AA92">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB92">
         <v>8000</v>
@@ -8696,7 +8696,7 @@
         <v>115</v>
       </c>
       <c r="AA93">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB93">
         <v>8000</v>
@@ -8779,7 +8779,7 @@
         <v>115</v>
       </c>
       <c r="AA94">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB94">
         <v>8000</v>
@@ -8862,7 +8862,7 @@
         <v>115</v>
       </c>
       <c r="AA95">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB95">
         <v>8000</v>
@@ -8945,7 +8945,7 @@
         <v>115</v>
       </c>
       <c r="AA96">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB96">
         <v>8000</v>
@@ -9031,7 +9031,7 @@
         <v>115</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -9114,7 +9114,7 @@
         <v>115</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -9200,7 +9200,7 @@
         <v>115</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -9295,7 +9295,7 @@
         <v>115</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -9378,7 +9378,7 @@
         <v>115</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -9467,7 +9467,7 @@
         <v>115</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -9556,7 +9556,7 @@
         <v>115</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -9639,7 +9639,7 @@
         <v>115</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -9731,7 +9731,7 @@
         <v>115</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -9817,7 +9817,7 @@
         <v>115</v>
       </c>
       <c r="AA106">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AB106">
         <v>8000</v>
@@ -10935,7 +10935,7 @@
         <v>115</v>
       </c>
       <c r="AA119">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB119">
         <v>8000</v>
@@ -11018,7 +11018,7 @@
         <v>115</v>
       </c>
       <c r="AA120">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB120">
         <v>8000</v>
@@ -11104,7 +11104,7 @@
         <v>115</v>
       </c>
       <c r="AA121">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB121">
         <v>8000</v>
@@ -11187,7 +11187,7 @@
         <v>115</v>
       </c>
       <c r="AA122">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB122">
         <v>8000</v>
@@ -11279,7 +11279,7 @@
         <v>115</v>
       </c>
       <c r="AA123">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB123">
         <v>8000</v>
@@ -11362,7 +11362,7 @@
         <v>115</v>
       </c>
       <c r="AA124">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB124">
         <v>8000</v>
@@ -11451,7 +11451,7 @@
         <v>115</v>
       </c>
       <c r="AA125">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB125">
         <v>8000</v>
@@ -11537,7 +11537,7 @@
         <v>115</v>
       </c>
       <c r="AA126">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB126">
         <v>8000</v>
@@ -11620,7 +11620,7 @@
         <v>115</v>
       </c>
       <c r="AA127">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB127">
         <v>8000</v>
@@ -11703,7 +11703,7 @@
         <v>115</v>
       </c>
       <c r="AA128">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB128">
         <v>8000</v>
@@ -11786,7 +11786,7 @@
         <v>115</v>
       </c>
       <c r="AA129">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB129">
         <v>8000</v>
@@ -11875,7 +11875,7 @@
         <v>115</v>
       </c>
       <c r="AA130">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB130">
         <v>8000</v>
@@ -15742,7 +15742,7 @@
         <v>115</v>
       </c>
       <c r="AA175">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB175">
         <v>8000</v>
@@ -15825,7 +15825,7 @@
         <v>115</v>
       </c>
       <c r="AA176">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB176">
         <v>8000</v>
@@ -15908,7 +15908,7 @@
         <v>115</v>
       </c>
       <c r="AA177">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB177">
         <v>8000</v>
@@ -15994,7 +15994,7 @@
         <v>115</v>
       </c>
       <c r="AA178">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB178">
         <v>8000</v>
@@ -16077,7 +16077,7 @@
         <v>115</v>
       </c>
       <c r="AA179">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB179">
         <v>8000</v>
@@ -16160,7 +16160,7 @@
         <v>115</v>
       </c>
       <c r="AA180">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB180">
         <v>8000</v>
@@ -16243,7 +16243,7 @@
         <v>115</v>
       </c>
       <c r="AA181">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB181">
         <v>8000</v>
@@ -16326,7 +16326,7 @@
         <v>115</v>
       </c>
       <c r="AA182">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB182">
         <v>8000</v>
@@ -16415,7 +16415,7 @@
         <v>115</v>
       </c>
       <c r="AA183">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB183">
         <v>8000</v>
@@ -16504,7 +16504,7 @@
         <v>115</v>
       </c>
       <c r="AA184">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB184">
         <v>8000</v>
@@ -16593,7 +16593,7 @@
         <v>115</v>
       </c>
       <c r="AA185">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB185">
         <v>8000</v>
@@ -16682,7 +16682,7 @@
         <v>115</v>
       </c>
       <c r="AA186">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB186">
         <v>8000</v>
@@ -16771,7 +16771,7 @@
         <v>115</v>
       </c>
       <c r="AA187">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB187">
         <v>8000</v>
@@ -16854,7 +16854,7 @@
         <v>115</v>
       </c>
       <c r="AA188">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB188">
         <v>8000</v>
@@ -16946,7 +16946,7 @@
         <v>115</v>
       </c>
       <c r="AA189">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB189">
         <v>8000</v>
@@ -17038,7 +17038,7 @@
         <v>115</v>
       </c>
       <c r="AA190">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB190">
         <v>8000</v>
@@ -17124,7 +17124,7 @@
         <v>115</v>
       </c>
       <c r="AA191">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB191">
         <v>8000</v>
@@ -17216,7 +17216,7 @@
         <v>115</v>
       </c>
       <c r="AA192">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB192">
         <v>8000</v>
@@ -17299,7 +17299,7 @@
         <v>115</v>
       </c>
       <c r="AA193">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB193">
         <v>8000</v>
@@ -17388,7 +17388,7 @@
         <v>115</v>
       </c>
       <c r="AA194">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB194">
         <v>8000</v>
@@ -17477,7 +17477,7 @@
         <v>115</v>
       </c>
       <c r="AA195">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB195">
         <v>8000</v>
@@ -17566,7 +17566,7 @@
         <v>115</v>
       </c>
       <c r="AA196">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB196">
         <v>8000</v>
@@ -17655,7 +17655,7 @@
         <v>115</v>
       </c>
       <c r="AA197">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB197">
         <v>8000</v>
@@ -17744,7 +17744,7 @@
         <v>115</v>
       </c>
       <c r="AA198">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB198">
         <v>8000</v>
@@ -17833,7 +17833,7 @@
         <v>115</v>
       </c>
       <c r="AA199">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB199">
         <v>8000</v>
@@ -17925,7 +17925,7 @@
         <v>115</v>
       </c>
       <c r="AA200">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB200">
         <v>8000</v>
@@ -18014,7 +18014,7 @@
         <v>115</v>
       </c>
       <c r="AA201">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB201">
         <v>8000</v>
@@ -18103,7 +18103,7 @@
         <v>115</v>
       </c>
       <c r="AA202">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB202">
         <v>8000</v>
@@ -18192,7 +18192,7 @@
         <v>115</v>
       </c>
       <c r="AA203">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB203">
         <v>8000</v>
@@ -18275,7 +18275,7 @@
         <v>115</v>
       </c>
       <c r="AA204">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB204">
         <v>8000</v>
@@ -18364,7 +18364,7 @@
         <v>115</v>
       </c>
       <c r="AA205">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB205">
         <v>8000</v>
@@ -18456,7 +18456,7 @@
         <v>115</v>
       </c>
       <c r="AA206">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB206">
         <v>8000</v>
